--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295091</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127295089</v>
       </c>
       <c r="B3" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127295092</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127295088</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127295090</v>
       </c>
       <c r="B6" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127295083</v>
       </c>
       <c r="B7" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127295087</v>
       </c>
       <c r="B8" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127295086</v>
       </c>
       <c r="B9" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295091</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127295089</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127295092</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127295088</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127295090</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127295083</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127295087</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127295086</v>
       </c>
       <c r="B9" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295091</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127295089</v>
       </c>
       <c r="B3" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127295092</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127295088</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127295090</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127295083</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127295087</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127295086</v>
       </c>
       <c r="B9" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295091</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127295089</v>
       </c>
       <c r="B3" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127295092</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127295088</v>
       </c>
       <c r="B5" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127295090</v>
       </c>
       <c r="B6" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127295083</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127295087</v>
       </c>
       <c r="B8" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127295086</v>
       </c>
       <c r="B9" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295091</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127295089</v>
       </c>
       <c r="B3" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127295092</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127295088</v>
       </c>
       <c r="B5" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127295090</v>
       </c>
       <c r="B6" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127295083</v>
       </c>
       <c r="B7" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127295087</v>
       </c>
       <c r="B8" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127295086</v>
       </c>
       <c r="B9" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1449,6 +1449,588 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128360483</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>378077</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6744655</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128360473</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>377973</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6744518</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128360457</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>378096</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6744584</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128360459</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>378092</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6744612</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128360458</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>378074</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6744615</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128360486</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>378105</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6744574</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -1454,7 +1454,7 @@
         <v>128360483</v>
       </c>
       <c r="B10" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128360473</v>
       </c>
       <c r="B11" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128360457</v>
+        <v>128360459</v>
       </c>
       <c r="B12" t="n">
-        <v>79031</v>
+        <v>79650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>378096</v>
+        <v>378092</v>
       </c>
       <c r="R12" t="n">
-        <v>6744584</v>
+        <v>6744612</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128360459</v>
+        <v>128360457</v>
       </c>
       <c r="B13" t="n">
-        <v>79649</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>378092</v>
+        <v>378096</v>
       </c>
       <c r="R13" t="n">
-        <v>6744612</v>
+        <v>6744584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>128360458</v>
       </c>
       <c r="B14" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128360486</v>
       </c>
       <c r="B15" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -1454,7 +1454,7 @@
         <v>128360483</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128360473</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128360459</v>
       </c>
       <c r="B12" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128360457</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128360458</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128360486</v>
       </c>
       <c r="B15" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -1454,7 +1454,7 @@
         <v>128360483</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128360473</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128360459</v>
       </c>
       <c r="B12" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128360457</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128360458</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128360486</v>
       </c>
       <c r="B15" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -1454,7 +1454,7 @@
         <v>128360483</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128360473</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128360459</v>
       </c>
       <c r="B12" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128360457</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128360458</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128360486</v>
       </c>
       <c r="B15" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128360483</v>
+        <v>128360473</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>378077</v>
+        <v>377973</v>
       </c>
       <c r="R10" t="n">
-        <v>6744655</v>
+        <v>6744518</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128360473</v>
+        <v>128360483</v>
       </c>
       <c r="B11" t="n">
         <v>79089</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377973</v>
+        <v>378077</v>
       </c>
       <c r="R11" t="n">
-        <v>6744518</v>
+        <v>6744655</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128360459</v>
+        <v>128360457</v>
       </c>
       <c r="B12" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>378092</v>
+        <v>378096</v>
       </c>
       <c r="R12" t="n">
-        <v>6744612</v>
+        <v>6744584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128360457</v>
+        <v>128360459</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>378096</v>
+        <v>378092</v>
       </c>
       <c r="R13" t="n">
-        <v>6744584</v>
+        <v>6744612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128360473</v>
+        <v>128360483</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377973</v>
+        <v>378077</v>
       </c>
       <c r="R10" t="n">
-        <v>6744518</v>
+        <v>6744655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128360483</v>
+        <v>128360473</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>378077</v>
+        <v>377973</v>
       </c>
       <c r="R11" t="n">
-        <v>6744655</v>
+        <v>6744518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128360457</v>
+        <v>128360459</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>378096</v>
+        <v>378092</v>
       </c>
       <c r="R12" t="n">
-        <v>6744584</v>
+        <v>6744612</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128360459</v>
+        <v>128360457</v>
       </c>
       <c r="B13" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>378092</v>
+        <v>378096</v>
       </c>
       <c r="R13" t="n">
-        <v>6744612</v>
+        <v>6744584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>128360458</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128360486</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -1454,7 +1454,7 @@
         <v>128360483</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128360473</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128360459</v>
       </c>
       <c r="B12" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128360457</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128360458</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128360486</v>
       </c>
       <c r="B15" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128360459</v>
+        <v>128360457</v>
       </c>
       <c r="B12" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>378092</v>
+        <v>378096</v>
       </c>
       <c r="R12" t="n">
-        <v>6744612</v>
+        <v>6744584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128360457</v>
+        <v>128360459</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>378096</v>
+        <v>378092</v>
       </c>
       <c r="R13" t="n">
-        <v>6744584</v>
+        <v>6744612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128360483</v>
+        <v>128360473</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>378077</v>
+        <v>377973</v>
       </c>
       <c r="R10" t="n">
-        <v>6744655</v>
+        <v>6744518</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128360473</v>
+        <v>128360483</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377973</v>
+        <v>378077</v>
       </c>
       <c r="R11" t="n">
-        <v>6744518</v>
+        <v>6744655</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>128360457</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128360459</v>
       </c>
       <c r="B13" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128360458</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128360486</v>
       </c>
       <c r="B15" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295091</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127295089</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127295092</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127295088</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127295090</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127295083</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127295087</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127295086</v>
       </c>
       <c r="B9" t="n">
-        <v>78696</v>
+        <v>78678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127295091</v>
+        <v>127295085</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>378073</v>
+        <v>378110</v>
       </c>
       <c r="R2" t="n">
-        <v>6744692</v>
+        <v>6744522</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295089</v>
+        <v>127295086</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>378117</v>
+        <v>378052</v>
       </c>
       <c r="R3" t="n">
-        <v>6744597</v>
+        <v>6744526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295092</v>
+        <v>74111078</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Mellanmyren, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>378105</v>
+        <v>377851</v>
       </c>
       <c r="R4" t="n">
-        <v>6744674</v>
+        <v>6744666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2018-11-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2018-11-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295088</v>
+        <v>127295084</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>378118</v>
+        <v>378112</v>
       </c>
       <c r="R5" t="n">
-        <v>6744598</v>
+        <v>6744523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295090</v>
+        <v>127295091</v>
       </c>
       <c r="B6" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>378100</v>
+        <v>378073</v>
       </c>
       <c r="R6" t="n">
-        <v>6744589</v>
+        <v>6744692</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295083</v>
+        <v>127295092</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377855</v>
+        <v>378105</v>
       </c>
       <c r="R7" t="n">
-        <v>6744595</v>
+        <v>6744674</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,45 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295087</v>
+        <v>128360457</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>378090</v>
+        <v>378096</v>
       </c>
       <c r="R8" t="n">
-        <v>6744609</v>
+        <v>6744584</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,57 +1342,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295086</v>
+        <v>128360458</v>
       </c>
       <c r="B9" t="n">
-        <v>78696</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>378052</v>
+        <v>378074</v>
       </c>
       <c r="R9" t="n">
-        <v>6744526</v>
+        <v>6744615</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,12 +1439,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1454,11 +1454,11 @@
         <v>128360473</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1551,11 +1551,11 @@
         <v>128360483</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128360457</v>
+        <v>128360486</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>378096</v>
+        <v>378105</v>
       </c>
       <c r="R12" t="n">
-        <v>6744584</v>
+        <v>6744574</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128360459</v>
+        <v>127295087</v>
       </c>
       <c r="B13" t="n">
-        <v>79743</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,14 +1773,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>378092</v>
+        <v>378090</v>
       </c>
       <c r="R13" t="n">
-        <v>6744612</v>
+        <v>6744609</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1827,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128360458</v>
+        <v>127295088</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,34 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>378074</v>
+        <v>378118</v>
       </c>
       <c r="R14" t="n">
-        <v>6744615</v>
+        <v>6744598</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1924,22 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128360486</v>
+        <v>127295090</v>
       </c>
       <c r="B15" t="n">
-        <v>78881</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>378105</v>
+        <v>378100</v>
       </c>
       <c r="R15" t="n">
-        <v>6744574</v>
+        <v>6744589</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2021,15 +2021,403 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128360459</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>378092</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6744612</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Dick Östberg</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Dick Östberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>74111079</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mellanmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>377851</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6744666</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127295083</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>377855</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6744595</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127295089</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>378117</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6744597</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22604-2025 artfynd.xlsx
+++ b/artfynd/A 22604-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295085</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295086</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74111078</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295084</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295091</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295092</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360457</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360458</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360473</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360483</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360486</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295087</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295088</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295090</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360459</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74111079</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295083</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,8 +2508,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295089</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>